--- a/samples/수주취합/2026.09.29_납품예정 인천엔진.xlsx
+++ b/samples/수주취합/2026.09.29_납품예정 인천엔진.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="100">
   <si>
     <t>No</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>EA</t>
+  </si>
+  <si>
+    <t>KRW</t>
   </si>
   <si>
     <t>Z1</t>
@@ -1029,11 +1032,11 @@
       <c r="AA2" s="1">
         <v>46280.000601851854</v>
       </c>
-      <c r="AB2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>81</v>
+      <c r="AB2">
+        <v>8000</v>
+      </c>
+      <c r="AC2">
+        <v>80000</v>
       </c>
       <c r="AD2" t="s">
         <v>88</v>
@@ -1042,7 +1045,7 @@
         <v>81</v>
       </c>
       <c r="AF2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AG2" t="s">
         <v>81</v>
@@ -1084,7 +1087,7 @@
         <v>81</v>
       </c>
       <c r="AT2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AU2" t="s">
         <v>81</v>
@@ -1218,16 +1221,16 @@
         <v>82</v>
       </c>
       <c r="I3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J3" t="s">
         <v>84</v>
       </c>
       <c r="K3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -1274,11 +1277,11 @@
       <c r="AA3" s="1">
         <v>46280.000601851854</v>
       </c>
-      <c r="AB3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>81</v>
+      <c r="AB3">
+        <v>6000</v>
+      </c>
+      <c r="AC3">
+        <v>36000</v>
       </c>
       <c r="AD3" t="s">
         <v>88</v>
@@ -1287,7 +1290,7 @@
         <v>81</v>
       </c>
       <c r="AF3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AG3" t="s">
         <v>81</v>
@@ -1329,7 +1332,7 @@
         <v>81</v>
       </c>
       <c r="AT3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AU3" t="s">
         <v>81</v>
@@ -1463,7 +1466,7 @@
         <v>82</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J4" t="s">
         <v>84</v>
@@ -1502,7 +1505,7 @@
         <v>81</v>
       </c>
       <c r="V4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="W4" t="s">
         <v>81</v>
@@ -1519,11 +1522,11 @@
       <c r="AA4" s="1">
         <v>46285.000601851854</v>
       </c>
-      <c r="AB4" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>81</v>
+      <c r="AB4">
+        <v>8200</v>
+      </c>
+      <c r="AC4">
+        <v>24600</v>
       </c>
       <c r="AD4" t="s">
         <v>88</v>
@@ -1532,7 +1535,7 @@
         <v>81</v>
       </c>
       <c r="AF4" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AG4" t="s">
         <v>81</v>
@@ -1574,7 +1577,7 @@
         <v>81</v>
       </c>
       <c r="AT4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AU4" t="s">
         <v>81</v>
@@ -1708,16 +1711,16 @@
         <v>82</v>
       </c>
       <c r="I5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J5" t="s">
         <v>84</v>
       </c>
       <c r="K5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -1747,7 +1750,7 @@
         <v>81</v>
       </c>
       <c r="V5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="W5" t="s">
         <v>81</v>
@@ -1764,11 +1767,11 @@
       <c r="AA5" s="1">
         <v>46286.000601851854</v>
       </c>
-      <c r="AB5" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>81</v>
+      <c r="AB5">
+        <v>5500</v>
+      </c>
+      <c r="AC5">
+        <v>11000</v>
       </c>
       <c r="AD5" t="s">
         <v>88</v>
@@ -1777,7 +1780,7 @@
         <v>81</v>
       </c>
       <c r="AF5" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AG5" t="s">
         <v>81</v>
@@ -1819,7 +1822,7 @@
         <v>81</v>
       </c>
       <c r="AT5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AU5" t="s">
         <v>81</v>
